--- a/run_outputs/results.xlsx
+++ b/run_outputs/results.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="19">
   <si>
     <t>Cipher</t>
   </si>
@@ -33,9 +33,6 @@
   </si>
   <si>
     <t>CPU</t>
-  </si>
-  <si>
-    <t>GPU</t>
   </si>
   <si>
     <t>Speedup</t>
@@ -78,6 +75,12 @@
   </si>
   <si>
     <t>Thoughput (MB/s)</t>
+  </si>
+  <si>
+    <t>GPU_ECB</t>
+  </si>
+  <si>
+    <t>GPU_CTR</t>
   </si>
 </sst>
 </file>
@@ -133,14 +136,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -424,7 +427,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V29"/>
+  <dimension ref="A1:V35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
@@ -435,174 +438,174 @@
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="5"/>
+      <c r="U1" s="5"/>
+      <c r="V1" s="5"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3" t="s">
+      <c r="C2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3" t="s">
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
-      <c r="V2" s="3"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+      <c r="V2" s="5"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
-      <c r="C3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="V3" s="3"/>
+      <c r="C3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="T3" s="5"/>
+      <c r="U3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="V3" s="5"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>5</v>
+      <c r="A5" s="6" t="s">
+        <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>2</v>
@@ -669,9 +672,9 @@
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A6" s="4"/>
+      <c r="A6" s="6"/>
       <c r="B6" s="2" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C6">
         <v>2.3300000000000001E-2</v>
@@ -703,7 +706,7 @@
       <c r="L6">
         <v>6434.4342999999999</v>
       </c>
-      <c r="M6" s="5">
+      <c r="M6" s="3">
         <v>0.1608</v>
       </c>
       <c r="N6">
@@ -735,1061 +738,1397 @@
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
+      <c r="A7" s="6"/>
       <c r="B7" s="2" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C7">
+        <v>2.3400000000000001E-2</v>
+      </c>
+      <c r="D7">
+        <v>43.7316</v>
+      </c>
+      <c r="E7">
+        <v>2.3400000000000001E-2</v>
+      </c>
+      <c r="F7">
+        <v>43.748800000000003</v>
+      </c>
+      <c r="G7">
+        <v>4.19E-2</v>
+      </c>
+      <c r="H7">
+        <v>1562.4690000000001</v>
+      </c>
+      <c r="I7">
+        <v>4.19E-2</v>
+      </c>
+      <c r="J7">
+        <v>1562.376</v>
+      </c>
+      <c r="K7">
+        <v>0.16</v>
+      </c>
+      <c r="L7">
+        <v>6554.6489000000001</v>
+      </c>
+      <c r="M7" s="3">
+        <v>0.1603</v>
+      </c>
+      <c r="N7">
+        <v>6540.5190000000002</v>
+      </c>
+      <c r="O7">
+        <v>2.2501000000000002</v>
+      </c>
+      <c r="P7">
+        <v>7456.3600999999999</v>
+      </c>
+      <c r="Q7">
+        <v>2.2496999999999998</v>
+      </c>
+      <c r="R7">
+        <v>7457.5905000000002</v>
+      </c>
+      <c r="S7">
+        <v>8.9425000000000008</v>
+      </c>
+      <c r="T7">
+        <v>7540.5213999999996</v>
+      </c>
+      <c r="U7">
+        <v>8.9422999999999995</v>
+      </c>
+      <c r="V7">
+        <v>7504.6233000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A8" s="6"/>
+      <c r="B8" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8">
         <f>C5/C6</f>
         <v>29.798283261802574</v>
       </c>
-      <c r="D7">
+      <c r="D8">
         <f>D6/D5</f>
         <v>29.771953617684954</v>
       </c>
-      <c r="E7">
+      <c r="E8">
         <f>E5/E6</f>
         <v>29.850427350427349</v>
       </c>
-      <c r="F7">
+      <c r="F8">
         <f>F6/F5</f>
         <v>29.815484311050476</v>
       </c>
-      <c r="G7">
-        <f t="shared" ref="G7" si="0">G5/G6</f>
+      <c r="G8">
+        <f t="shared" ref="G8" si="0">G5/G6</f>
         <v>1074.9239904988124</v>
       </c>
-      <c r="H7">
-        <f t="shared" ref="H7" si="1">H6/H5</f>
+      <c r="H8">
+        <f t="shared" ref="H8" si="1">H6/H5</f>
         <v>1074.3714265985361</v>
       </c>
-      <c r="I7">
-        <f t="shared" ref="I7" si="2">I5/I6</f>
+      <c r="I8">
+        <f t="shared" ref="I8" si="2">I5/I6</f>
         <v>1104.1156626506024</v>
       </c>
-      <c r="J7">
-        <f t="shared" ref="J7" si="3">J6/J5</f>
+      <c r="J8">
+        <f t="shared" ref="J8" si="3">J6/J5</f>
         <v>1104.6280500594282</v>
       </c>
-      <c r="K7">
-        <f t="shared" ref="K7" si="4">K5/K6</f>
+      <c r="K8">
+        <f t="shared" ref="K8" si="4">K5/K6</f>
         <v>4427.8840490797547</v>
       </c>
-      <c r="L7">
-        <f t="shared" ref="L7" si="5">L6/L5</f>
+      <c r="L8">
+        <f t="shared" ref="L8" si="5">L6/L5</f>
         <v>4428.9883672907481</v>
       </c>
-      <c r="M7">
-        <f t="shared" ref="M7" si="6">M5/M6</f>
+      <c r="M8">
+        <f t="shared" ref="M8" si="6">M5/M6</f>
         <v>4543.7157960199002</v>
       </c>
-      <c r="N7">
-        <f t="shared" ref="N7" si="7">N6/N5</f>
+      <c r="N8">
+        <f t="shared" ref="N8" si="7">N6/N5</f>
         <v>4543.6142001114831</v>
       </c>
-      <c r="O7">
-        <f t="shared" ref="O7" si="8">O5/O6</f>
+      <c r="O8">
+        <f t="shared" ref="O8" si="8">O5/O6</f>
         <v>4717.7695615816519</v>
       </c>
-      <c r="P7">
-        <f t="shared" ref="P7" si="9">P6/P5</f>
+      <c r="P8">
+        <f t="shared" ref="P8" si="9">P6/P5</f>
         <v>4717.735611891816</v>
       </c>
-      <c r="Q7">
-        <f t="shared" ref="Q7" si="10">Q5/Q6</f>
+      <c r="Q8">
+        <f t="shared" ref="Q8" si="10">Q5/Q6</f>
         <v>4814.9136984654842</v>
       </c>
-      <c r="R7">
-        <f t="shared" ref="R7" si="11">R6/R5</f>
+      <c r="R8">
+        <f t="shared" ref="R8" si="11">R6/R5</f>
         <v>4814.7816775302626</v>
       </c>
-      <c r="S7">
-        <f t="shared" ref="S7" si="12">S5/S6</f>
+      <c r="S8">
+        <f t="shared" ref="S8" si="12">S5/S6</f>
         <v>5271.7120554976518</v>
       </c>
-      <c r="T7">
-        <f t="shared" ref="T7" si="13">T6/T5</f>
+      <c r="T8">
+        <f t="shared" ref="T8" si="13">T6/T5</f>
         <v>5271.5739118244901</v>
       </c>
-      <c r="U7">
-        <f t="shared" ref="U7" si="14">U5/U6</f>
+      <c r="U8">
+        <f t="shared" ref="U8" si="14">U5/U6</f>
         <v>59.232686453576861</v>
       </c>
-      <c r="V7">
-        <f t="shared" ref="V7" si="15">V6/V5</f>
+      <c r="V8">
+        <f t="shared" ref="V8" si="15">V6/V5</f>
         <v>5304.4598488593829</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="2" t="s">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C8">
+      <c r="C9">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="D8">
+      <c r="D9">
         <v>1178.5260000000001</v>
       </c>
-      <c r="E8">
+      <c r="E9">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="F8">
+      <c r="F9">
         <v>890.06020000000001</v>
       </c>
-      <c r="G8">
+      <c r="G9">
         <v>5.4100000000000002E-2</v>
       </c>
-      <c r="H8">
+      <c r="H9">
         <v>1211.7537</v>
       </c>
-      <c r="I8">
+      <c r="I9">
         <v>7.1900000000000006E-2</v>
       </c>
-      <c r="J8">
+      <c r="J9">
         <v>912.00649999999996</v>
       </c>
-      <c r="K8">
+      <c r="K9">
         <v>0.94299999999999995</v>
       </c>
-      <c r="L8">
+      <c r="L9">
         <v>1112.0155999999999</v>
       </c>
-      <c r="M8">
+      <c r="M9">
         <v>1.2210000000000001</v>
       </c>
-      <c r="N8">
+      <c r="N9">
         <v>858.79110000000003</v>
       </c>
-      <c r="O8">
+      <c r="O9">
         <v>15.5174</v>
       </c>
-      <c r="P8">
+      <c r="P9">
         <v>1081.1893</v>
       </c>
-      <c r="Q8">
+      <c r="Q9">
         <v>19.549700000000001</v>
       </c>
-      <c r="R8">
+      <c r="R9">
         <v>858.18349999999998</v>
       </c>
-      <c r="S8">
+      <c r="S9">
         <v>60.403500000000001</v>
       </c>
-      <c r="T8">
+      <c r="T9">
         <v>1111.0091</v>
       </c>
-      <c r="U8">
+      <c r="U9">
         <v>77.887600000000006</v>
       </c>
-      <c r="V8">
+      <c r="V9">
         <v>861.61189999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A9" s="4"/>
-      <c r="B9" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A10" s="6"/>
+      <c r="B10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10">
         <v>1.8E-3</v>
       </c>
-      <c r="D9">
+      <c r="D10">
         <v>571.42859999999996</v>
       </c>
-      <c r="E9">
+      <c r="E10">
         <v>1.9E-3</v>
       </c>
-      <c r="F9">
+      <c r="F10">
         <v>549.90380000000005</v>
       </c>
-      <c r="G9">
+      <c r="G10">
         <v>1.9E-3</v>
       </c>
-      <c r="H9">
+      <c r="H10">
         <v>34320.954299999998</v>
       </c>
-      <c r="I9">
+      <c r="I10">
         <v>1.9E-3</v>
       </c>
-      <c r="J9">
+      <c r="J10">
         <v>34042.552900000002</v>
       </c>
-      <c r="K9">
+      <c r="K10">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="L9">
+      <c r="L10">
         <v>225986.2052</v>
       </c>
-      <c r="M9">
+      <c r="M10">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="N9">
+      <c r="N10">
         <v>235402.29790000001</v>
       </c>
-      <c r="O9">
+      <c r="O10">
         <v>2.0199999999999999E-2</v>
       </c>
-      <c r="P9">
+      <c r="P10">
         <v>830621.04920000001</v>
       </c>
-      <c r="Q9">
+      <c r="Q10">
         <v>1.5299999999999999E-2</v>
       </c>
-      <c r="R9">
+      <c r="R10">
         <v>1096378.0903</v>
       </c>
-      <c r="S9">
+      <c r="S10">
         <v>0.1885</v>
       </c>
-      <c r="T9">
+      <c r="T10">
         <v>356004.61940000003</v>
       </c>
-      <c r="U9">
+      <c r="U10">
         <v>0.13880000000000001</v>
       </c>
-      <c r="V9">
+      <c r="V10">
         <v>483326.11969999998</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A10" s="4"/>
-      <c r="B10" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10">
-        <f>C8/C9</f>
-        <v>0.5</v>
-      </c>
-      <c r="D10">
-        <f>D9/D8</f>
-        <v>0.48486719851747007</v>
-      </c>
-      <c r="E10">
-        <f>E8/E9</f>
-        <v>0.63157894736842102</v>
-      </c>
-      <c r="F10">
-        <f>F9/F8</f>
-        <v>0.61782764806245694</v>
-      </c>
-      <c r="G10">
-        <f t="shared" ref="G10" si="16">G8/G9</f>
-        <v>28.473684210526319</v>
-      </c>
-      <c r="H10">
-        <f t="shared" ref="H10" si="17">H9/H8</f>
-        <v>28.323374873953345</v>
-      </c>
-      <c r="I10">
-        <f t="shared" ref="I10" si="18">I8/I9</f>
-        <v>37.842105263157897</v>
-      </c>
-      <c r="J10">
-        <f t="shared" ref="J10" si="19">J9/J8</f>
-        <v>37.32709459855824</v>
-      </c>
-      <c r="K10">
-        <f t="shared" ref="K10" si="20">K8/K9</f>
-        <v>205</v>
-      </c>
-      <c r="L10">
-        <f t="shared" ref="L10" si="21">L9/L8</f>
-        <v>203.22215371798742</v>
-      </c>
-      <c r="M10">
-        <f t="shared" ref="M10" si="22">M8/M9</f>
-        <v>271.33333333333337</v>
-      </c>
-      <c r="N10">
-        <f t="shared" ref="N10" si="23">N9/N8</f>
-        <v>274.10891647572964</v>
-      </c>
-      <c r="O10">
-        <f t="shared" ref="O10" si="24">O8/O9</f>
-        <v>768.18811881188128</v>
-      </c>
-      <c r="P10">
-        <f t="shared" ref="P10" si="25">P9/P8</f>
-        <v>768.24756700792364</v>
-      </c>
-      <c r="Q10">
-        <f t="shared" ref="Q10" si="26">Q8/Q9</f>
-        <v>1277.7581699346406</v>
-      </c>
-      <c r="R10">
-        <f t="shared" ref="R10" si="27">R9/R8</f>
-        <v>1277.5567117055969</v>
-      </c>
-      <c r="S10">
-        <f t="shared" ref="S10" si="28">S8/S9</f>
-        <v>320.44297082228115</v>
-      </c>
-      <c r="T10">
-        <f t="shared" ref="T10" si="29">T9/T8</f>
-        <v>320.43357646665544</v>
-      </c>
-      <c r="U10">
-        <f t="shared" ref="U10" si="30">U8/U9</f>
-        <v>561.14985590778099</v>
-      </c>
-      <c r="V10">
-        <f t="shared" ref="V10" si="31">V9/V8</f>
-        <v>560.95571532844428</v>
-      </c>
-    </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="A11" s="6"/>
       <c r="B11" s="2" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C11">
-        <v>4.2799999999999998E-2</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="D11">
-        <v>23.9206</v>
+        <v>603.25</v>
       </c>
       <c r="E11">
-        <v>6.8099999999999994E-2</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="F11">
-        <v>15.0428</v>
+        <v>599.5204</v>
       </c>
       <c r="G11">
-        <v>2.7645</v>
+        <v>1.9E-3</v>
       </c>
       <c r="H11">
-        <v>23.7059</v>
+        <v>35210.784099999997</v>
       </c>
       <c r="I11">
-        <v>4.3960999999999997</v>
+        <v>1.8E-3</v>
       </c>
       <c r="J11">
-        <v>14.9077</v>
+        <v>36734.108800000002</v>
       </c>
       <c r="K11">
-        <v>44.857100000000003</v>
+        <v>4.7000000000000002E-3</v>
       </c>
       <c r="L11">
-        <v>23.375900000000001</v>
+        <v>221106.60949999999</v>
       </c>
       <c r="M11">
-        <v>69.989999999999995</v>
+        <v>4.3E-3</v>
       </c>
       <c r="N11">
-        <v>14.9817</v>
+        <v>246375.94</v>
       </c>
       <c r="O11">
-        <v>710.48760000000004</v>
+        <v>2.06E-2</v>
       </c>
       <c r="P11">
-        <v>23.613700000000001</v>
+        <v>815631.61250000005</v>
       </c>
       <c r="Q11">
-        <v>1127.1425999999999</v>
+        <v>1.5800000000000002E-2</v>
       </c>
       <c r="R11">
-        <v>14.8847</v>
+        <v>1065193.0251</v>
       </c>
       <c r="S11">
-        <v>2840.0414999999998</v>
+        <v>0.187</v>
       </c>
       <c r="T11">
-        <v>23.6295</v>
+        <v>358966.13630000001</v>
       </c>
       <c r="U11">
-        <v>4502.7228999999998</v>
+        <v>0.13980000000000001</v>
       </c>
       <c r="V11">
-        <v>14.9041</v>
+        <v>479875.52250000002</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A12" s="4"/>
+      <c r="A12" s="6"/>
       <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C12">
+        <f>C9/C10</f>
+        <v>0.5</v>
+      </c>
+      <c r="D12">
+        <f>D10/D9</f>
+        <v>0.48486719851747007</v>
+      </c>
+      <c r="E12">
+        <f>E9/E10</f>
+        <v>0.63157894736842102</v>
+      </c>
+      <c r="F12">
+        <f>F10/F9</f>
+        <v>0.61782764806245694</v>
+      </c>
+      <c r="G12">
+        <f t="shared" ref="G12" si="16">G9/G10</f>
+        <v>28.473684210526319</v>
+      </c>
+      <c r="H12">
+        <f t="shared" ref="H12" si="17">H10/H9</f>
+        <v>28.323374873953345</v>
+      </c>
+      <c r="I12">
+        <f t="shared" ref="I12" si="18">I9/I10</f>
+        <v>37.842105263157897</v>
+      </c>
+      <c r="J12">
+        <f t="shared" ref="J12" si="19">J10/J9</f>
+        <v>37.32709459855824</v>
+      </c>
+      <c r="K12">
+        <f t="shared" ref="K12" si="20">K9/K10</f>
+        <v>205</v>
+      </c>
+      <c r="L12">
+        <f t="shared" ref="L12" si="21">L10/L9</f>
+        <v>203.22215371798742</v>
+      </c>
+      <c r="M12">
+        <f t="shared" ref="M12" si="22">M9/M10</f>
+        <v>271.33333333333337</v>
+      </c>
+      <c r="N12">
+        <f t="shared" ref="N12" si="23">N10/N9</f>
+        <v>274.10891647572964</v>
+      </c>
+      <c r="O12">
+        <f t="shared" ref="O12" si="24">O9/O10</f>
+        <v>768.18811881188128</v>
+      </c>
+      <c r="P12">
+        <f t="shared" ref="P12" si="25">P10/P9</f>
+        <v>768.24756700792364</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" ref="Q12" si="26">Q9/Q10</f>
+        <v>1277.7581699346406</v>
+      </c>
+      <c r="R12">
+        <f t="shared" ref="R12" si="27">R10/R9</f>
+        <v>1277.5567117055969</v>
+      </c>
+      <c r="S12">
+        <f t="shared" ref="S12" si="28">S9/S10</f>
+        <v>320.44297082228115</v>
+      </c>
+      <c r="T12">
+        <f t="shared" ref="T12" si="29">T10/T9</f>
+        <v>320.43357646665544</v>
+      </c>
+      <c r="U12">
+        <f t="shared" ref="U12" si="30">U9/U10</f>
+        <v>561.14985590778099</v>
+      </c>
+      <c r="V12">
+        <f t="shared" ref="V12" si="31">V10/V9</f>
+        <v>560.95571532844428</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>4.2799999999999998E-2</v>
+      </c>
+      <c r="D13">
+        <v>23.9206</v>
+      </c>
+      <c r="E13">
+        <v>6.8099999999999994E-2</v>
+      </c>
+      <c r="F13">
+        <v>15.0428</v>
+      </c>
+      <c r="G13">
+        <v>2.7645</v>
+      </c>
+      <c r="H13">
+        <v>23.7059</v>
+      </c>
+      <c r="I13">
+        <v>4.3960999999999997</v>
+      </c>
+      <c r="J13">
+        <v>14.9077</v>
+      </c>
+      <c r="K13">
+        <v>44.857100000000003</v>
+      </c>
+      <c r="L13">
+        <v>23.375900000000001</v>
+      </c>
+      <c r="M13">
+        <v>69.989999999999995</v>
+      </c>
+      <c r="N13">
+        <v>14.9817</v>
+      </c>
+      <c r="O13">
+        <v>710.48760000000004</v>
+      </c>
+      <c r="P13">
+        <v>23.613700000000001</v>
+      </c>
+      <c r="Q13">
+        <v>1127.1425999999999</v>
+      </c>
+      <c r="R13">
+        <v>14.8847</v>
+      </c>
+      <c r="S13">
+        <v>2840.0414999999998</v>
+      </c>
+      <c r="T13">
+        <v>23.6295</v>
+      </c>
+      <c r="U13">
+        <v>4502.7228999999998</v>
+      </c>
+      <c r="V13">
+        <v>14.9041</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A14" s="6"/>
+      <c r="B14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14">
         <v>1.1599999999999999E-2</v>
       </c>
-      <c r="D12">
+      <c r="D14">
         <v>88.514700000000005</v>
       </c>
-      <c r="E12">
+      <c r="E14">
         <v>1.1299999999999999E-2</v>
       </c>
-      <c r="F12">
+      <c r="F14">
         <v>90.995900000000006</v>
       </c>
-      <c r="G12">
+      <c r="G14">
         <v>2.01E-2</v>
       </c>
-      <c r="H12">
+      <c r="H14">
         <v>3257.4947000000002</v>
       </c>
-      <c r="I12">
+      <c r="I14">
         <v>1.89E-2</v>
       </c>
-      <c r="J12">
+      <c r="J14">
         <v>3476.3243000000002</v>
       </c>
-      <c r="K12">
+      <c r="K14">
         <v>0.04</v>
       </c>
-      <c r="L12">
+      <c r="L14">
         <v>26222.791499999999</v>
       </c>
-      <c r="M12">
+      <c r="M14">
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="N12">
+      <c r="N14">
         <v>27997.264899999998</v>
       </c>
-      <c r="O12">
+      <c r="O14">
         <v>0.51649999999999996</v>
       </c>
-      <c r="P12">
+      <c r="P14">
         <v>32483.7667</v>
       </c>
-      <c r="Q12">
+      <c r="Q14">
         <v>0.4763</v>
       </c>
-      <c r="R12">
+      <c r="R14">
         <v>35223.520400000001</v>
       </c>
-      <c r="S12">
+      <c r="S14">
         <v>2.0545</v>
       </c>
-      <c r="T12">
+      <c r="T14">
         <v>32664.190200000001</v>
       </c>
-      <c r="U12">
+      <c r="U14">
         <v>1.8939999999999999</v>
       </c>
-      <c r="V12">
+      <c r="V14">
         <v>35432.286500000002</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A13" s="4"/>
-      <c r="B13" s="2" t="s">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A15" s="6"/>
+      <c r="B15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15">
+        <v>1.03E-2</v>
+      </c>
+      <c r="D15">
+        <v>99.727599999999995</v>
+      </c>
+      <c r="E15">
+        <v>1.04E-2</v>
+      </c>
+      <c r="F15">
+        <v>98.6601</v>
+      </c>
+      <c r="G15">
+        <v>2.9899999999999999E-2</v>
+      </c>
+      <c r="H15">
+        <v>2191.6118999999999</v>
+      </c>
+      <c r="I15">
+        <v>2.9899999999999999E-2</v>
+      </c>
+      <c r="J15">
+        <v>2190.2806999999998</v>
+      </c>
+      <c r="K15">
+        <v>5.96E-2</v>
+      </c>
+      <c r="L15">
+        <v>17605.845499999999</v>
+      </c>
+      <c r="M15">
+        <v>5.9400000000000001E-2</v>
+      </c>
+      <c r="N15">
+        <v>17655.171999999999</v>
+      </c>
+      <c r="O15">
+        <v>0.81620000000000004</v>
+      </c>
+      <c r="P15">
+        <v>20554.832399999999</v>
+      </c>
+      <c r="Q15">
+        <v>0.81540000000000001</v>
+      </c>
+      <c r="R15">
+        <v>20576.4519</v>
+      </c>
+      <c r="S15">
+        <v>3.2528999999999999</v>
+      </c>
+      <c r="T15">
+        <v>20630.2546</v>
+      </c>
+      <c r="U15">
+        <v>3.2515999999999998</v>
+      </c>
+      <c r="V15">
+        <v>20638.781900000002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A16" s="6"/>
+      <c r="B16" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16">
+        <f>C13/C14</f>
+        <v>3.6896551724137931</v>
+      </c>
+      <c r="D16">
+        <f>D14/D13</f>
+        <v>3.7003545061578724</v>
+      </c>
+      <c r="E16">
+        <f>E13/E14</f>
+        <v>6.0265486725663715</v>
+      </c>
+      <c r="F16">
+        <f>F14/F13</f>
+        <v>6.0491331401068953</v>
+      </c>
+      <c r="G16">
+        <f t="shared" ref="G16" si="32">G13/G14</f>
+        <v>137.53731343283582</v>
+      </c>
+      <c r="H16">
+        <f t="shared" ref="H16" si="33">H14/H13</f>
+        <v>137.41282549913734</v>
+      </c>
+      <c r="I16">
+        <f t="shared" ref="I16" si="34">I13/I14</f>
+        <v>232.59788359788357</v>
+      </c>
+      <c r="J16">
+        <f t="shared" ref="J16" si="35">J14/J13</f>
+        <v>233.18984819925274</v>
+      </c>
+      <c r="K16">
+        <f t="shared" ref="K16" si="36">K13/K14</f>
+        <v>1121.4275</v>
+      </c>
+      <c r="L16">
+        <f t="shared" ref="L16" si="37">L14/L13</f>
+        <v>1121.7874605897525</v>
+      </c>
+      <c r="M16">
+        <f t="shared" ref="M16" si="38">M13/M14</f>
+        <v>1866.3999999999999</v>
+      </c>
+      <c r="N16">
+        <f t="shared" ref="N16" si="39">N14/N13</f>
+        <v>1868.7642190138636</v>
+      </c>
+      <c r="O16">
+        <f t="shared" ref="O16" si="40">O13/O14</f>
+        <v>1375.5810261374638</v>
+      </c>
+      <c r="P16">
+        <f t="shared" ref="P16" si="41">P14/P13</f>
+        <v>1375.6322262076676</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" ref="Q16" si="42">Q13/Q14</f>
+        <v>2366.4551753096785</v>
+      </c>
+      <c r="R16">
+        <f t="shared" ref="R16" si="43">R14/R13</f>
+        <v>2366.4246105060902</v>
+      </c>
+      <c r="S16">
+        <f t="shared" ref="S16" si="44">S13/S14</f>
+        <v>1382.3516670722802</v>
+      </c>
+      <c r="T16">
+        <f t="shared" ref="T16" si="45">T14/T13</f>
+        <v>1382.3479210309147</v>
+      </c>
+      <c r="U16">
+        <f t="shared" ref="U16" si="46">U13/U14</f>
+        <v>2377.3616156282997</v>
+      </c>
+      <c r="V16">
+        <f t="shared" ref="V16" si="47">V14/V13</f>
+        <v>2377.3516347850591</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="4"/>
+      <c r="R21" s="4"/>
+      <c r="S21" s="4"/>
+      <c r="T21" s="4"/>
+      <c r="U21" s="4"/>
+      <c r="V21" s="4"/>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" s="5"/>
+      <c r="F22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22" s="5"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J22" s="5"/>
+      <c r="L22" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="M22" s="5"/>
+      <c r="N22" s="4"/>
+      <c r="O22" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="4"/>
+      <c r="R22" s="4"/>
+      <c r="V22" s="4"/>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L23" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="O23" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="P23" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="R23" s="4"/>
+      <c r="V23" s="4"/>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A24" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C13">
-        <f>C11/C12</f>
-        <v>3.6896551724137931</v>
-      </c>
-      <c r="D13">
-        <f>D12/D11</f>
-        <v>3.7003545061578724</v>
-      </c>
-      <c r="E13">
-        <f>E11/E12</f>
-        <v>6.0265486725663715</v>
-      </c>
-      <c r="F13">
-        <f>F12/F11</f>
-        <v>6.0491331401068953</v>
-      </c>
-      <c r="G13">
-        <f t="shared" ref="G13" si="32">G11/G12</f>
-        <v>137.53731343283582</v>
-      </c>
-      <c r="H13">
-        <f t="shared" ref="H13" si="33">H12/H11</f>
-        <v>137.41282549913734</v>
-      </c>
-      <c r="I13">
-        <f t="shared" ref="I13" si="34">I11/I12</f>
-        <v>232.59788359788357</v>
-      </c>
-      <c r="J13">
-        <f t="shared" ref="J13" si="35">J12/J11</f>
-        <v>233.18984819925274</v>
-      </c>
-      <c r="K13">
-        <f t="shared" ref="K13" si="36">K11/K12</f>
-        <v>1121.4275</v>
-      </c>
-      <c r="L13">
-        <f t="shared" ref="L13" si="37">L12/L11</f>
-        <v>1121.7874605897525</v>
-      </c>
-      <c r="M13">
-        <f t="shared" ref="M13" si="38">M11/M12</f>
-        <v>1866.3999999999999</v>
-      </c>
-      <c r="N13">
-        <f t="shared" ref="N13" si="39">N12/N11</f>
-        <v>1868.7642190138636</v>
-      </c>
-      <c r="O13">
-        <f t="shared" ref="O13" si="40">O11/O12</f>
-        <v>1375.5810261374638</v>
-      </c>
-      <c r="P13">
-        <f t="shared" ref="P13" si="41">P12/P11</f>
-        <v>1375.6322262076676</v>
-      </c>
-      <c r="Q13">
-        <f t="shared" ref="Q13" si="42">Q11/Q12</f>
-        <v>2366.4551753096785</v>
-      </c>
-      <c r="R13">
-        <f t="shared" ref="R13" si="43">R12/R11</f>
-        <v>2366.4246105060902</v>
-      </c>
-      <c r="S13">
-        <f t="shared" ref="S13" si="44">S11/S12</f>
-        <v>1382.3516670722802</v>
-      </c>
-      <c r="T13">
-        <f t="shared" ref="T13" si="45">T12/T11</f>
-        <v>1382.3479210309147</v>
-      </c>
-      <c r="U13">
-        <f t="shared" ref="U13" si="46">U11/U12</f>
-        <v>2377.3616156282997</v>
-      </c>
-      <c r="V13">
-        <f t="shared" ref="V13" si="47">V12/V11</f>
-        <v>2377.3516347850591</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="6"/>
-      <c r="R18" s="6"/>
-      <c r="S18" s="6"/>
-      <c r="T18" s="6"/>
-      <c r="U18" s="6"/>
-      <c r="V18" s="6"/>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="F19" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19" s="3"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J19" s="3"/>
-      <c r="L19" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="M19" s="3"/>
-      <c r="N19" s="6"/>
-      <c r="O19" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="6"/>
-      <c r="R19" s="6"/>
-      <c r="V19" s="6"/>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="L20" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="M20" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="O20" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="P20" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="R20" s="6"/>
-      <c r="V20" s="6"/>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B21" s="2" t="s">
+      <c r="B24" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C21">
+      <c r="C24">
         <f>D5</f>
         <v>1.4746999999999999</v>
       </c>
-      <c r="D21">
+      <c r="D24">
         <f>F5</f>
         <v>1.466</v>
       </c>
-      <c r="F21">
+      <c r="F24">
         <f>H5</f>
         <v>1.4481999999999999</v>
       </c>
-      <c r="G21">
+      <c r="G24">
         <f>J5</f>
         <v>1.4302999999999999</v>
       </c>
-      <c r="I21">
+      <c r="I24">
         <f>L5</f>
         <v>1.4528000000000001</v>
       </c>
-      <c r="J21">
+      <c r="J24">
         <f>N5</f>
         <v>1.4352</v>
       </c>
-      <c r="L21">
+      <c r="L24">
         <f>P5</f>
         <v>1.4160999999999999</v>
       </c>
-      <c r="M21">
+      <c r="M24">
         <f>R5</f>
         <v>1.3960999999999999</v>
       </c>
-      <c r="O21">
+      <c r="O24">
         <f>T5</f>
         <v>1.4267000000000001</v>
       </c>
-      <c r="P21">
+      <c r="P24">
         <f>V5</f>
         <v>1.4158999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A22" s="4"/>
-      <c r="B22" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C22">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A25" s="6"/>
+      <c r="B25" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25">
         <f>D6</f>
         <v>43.904699999999998</v>
       </c>
-      <c r="D22">
+      <c r="D25">
         <f>F6</f>
         <v>43.709499999999998</v>
       </c>
-      <c r="F22">
+      <c r="F25">
         <f>H6</f>
         <v>1555.9047</v>
       </c>
-      <c r="G22">
+      <c r="G25">
         <f>J6</f>
         <v>1579.9494999999999</v>
       </c>
-      <c r="I22">
+      <c r="I25">
         <f>L6</f>
         <v>6434.4342999999999</v>
       </c>
-      <c r="J22">
+      <c r="J25">
         <f>N6</f>
         <v>6520.9951000000001</v>
       </c>
-      <c r="L22">
+      <c r="L25">
         <f>P6</f>
         <v>6680.7853999999998</v>
       </c>
-      <c r="M22">
+      <c r="M25">
         <f>R6</f>
         <v>6721.9166999999998</v>
       </c>
-      <c r="O22">
+      <c r="O25">
         <f>T6</f>
         <v>7520.9544999999998</v>
       </c>
-      <c r="P22">
+      <c r="P25">
         <f>V6</f>
         <v>7510.5847000000003</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A23" s="4"/>
-      <c r="B23" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23">
-        <f>C22/C21</f>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A26" s="6"/>
+      <c r="B26" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26">
+        <f>D7</f>
+        <v>43.7316</v>
+      </c>
+      <c r="D26">
+        <f>F7</f>
+        <v>43.748800000000003</v>
+      </c>
+      <c r="F26">
+        <f>H7</f>
+        <v>1562.4690000000001</v>
+      </c>
+      <c r="G26">
+        <f>J7</f>
+        <v>1562.376</v>
+      </c>
+      <c r="I26">
+        <f>L7</f>
+        <v>6554.6489000000001</v>
+      </c>
+      <c r="J26">
+        <f>N7</f>
+        <v>6540.5190000000002</v>
+      </c>
+      <c r="L26">
+        <f>P7</f>
+        <v>7456.3600999999999</v>
+      </c>
+      <c r="M26">
+        <f>R7</f>
+        <v>7457.5905000000002</v>
+      </c>
+      <c r="O26">
+        <f>T7</f>
+        <v>7540.5213999999996</v>
+      </c>
+      <c r="P26">
+        <f>V7</f>
+        <v>7504.6233000000002</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A27" s="6"/>
+      <c r="B27" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C27">
+        <f>C25/C24</f>
         <v>29.771953617684954</v>
       </c>
-      <c r="D23">
-        <f>D22/D21</f>
+      <c r="D27">
+        <f>D25/D24</f>
         <v>29.815484311050476</v>
       </c>
-      <c r="F23">
-        <f t="shared" ref="F23" si="48">F22/F21</f>
+      <c r="F27">
+        <f t="shared" ref="F27" si="48">F25/F24</f>
         <v>1074.3714265985361</v>
       </c>
-      <c r="G23">
-        <f t="shared" ref="G23" si="49">G22/G21</f>
+      <c r="G27">
+        <f t="shared" ref="G27" si="49">G25/G24</f>
         <v>1104.6280500594282</v>
       </c>
-      <c r="I23">
-        <f t="shared" ref="I23" si="50">I22/I21</f>
+      <c r="I27">
+        <f t="shared" ref="I27" si="50">I25/I24</f>
         <v>4428.9883672907481</v>
       </c>
-      <c r="J23">
-        <f t="shared" ref="J23" si="51">J22/J21</f>
+      <c r="J27">
+        <f t="shared" ref="J27" si="51">J25/J24</f>
         <v>4543.6142001114831</v>
       </c>
-      <c r="L23">
-        <f t="shared" ref="L23" si="52">L22/L21</f>
+      <c r="L27">
+        <f t="shared" ref="L27" si="52">L25/L24</f>
         <v>4717.735611891816</v>
       </c>
-      <c r="M23">
-        <f t="shared" ref="M23" si="53">M22/M21</f>
+      <c r="M27">
+        <f t="shared" ref="M27" si="53">M25/M24</f>
         <v>4814.7816775302626</v>
       </c>
-      <c r="O23">
-        <f t="shared" ref="O23" si="54">O22/O21</f>
+      <c r="O27">
+        <f t="shared" ref="O27" si="54">O25/O24</f>
         <v>5271.5739118244901</v>
       </c>
-      <c r="P23">
-        <f t="shared" ref="P23" si="55">P22/P21</f>
+      <c r="P27">
+        <f t="shared" ref="P27" si="55">P25/P24</f>
         <v>5304.4598488593829</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28">
+        <f>D9</f>
+        <v>1178.5260000000001</v>
+      </c>
+      <c r="D28">
+        <f>F9</f>
+        <v>890.06020000000001</v>
+      </c>
+      <c r="F28">
+        <f>H9</f>
+        <v>1211.7537</v>
+      </c>
+      <c r="G28">
+        <f>J9</f>
+        <v>912.00649999999996</v>
+      </c>
+      <c r="I28">
+        <f>L9</f>
+        <v>1112.0155999999999</v>
+      </c>
+      <c r="J28">
+        <f>N9</f>
+        <v>858.79110000000003</v>
+      </c>
+      <c r="L28">
+        <f>P9</f>
+        <v>1081.1893</v>
+      </c>
+      <c r="M28">
+        <f>R9</f>
+        <v>858.18349999999998</v>
+      </c>
+      <c r="O28">
+        <v>1111.0091</v>
+      </c>
+      <c r="P28">
+        <f>V9</f>
+        <v>861.61189999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A29" s="6"/>
+      <c r="B29" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29">
+        <f>D10</f>
+        <v>571.42859999999996</v>
+      </c>
+      <c r="D29">
+        <f>F10</f>
+        <v>549.90380000000005</v>
+      </c>
+      <c r="F29">
+        <f>H10</f>
+        <v>34320.954299999998</v>
+      </c>
+      <c r="G29">
+        <f>J10</f>
+        <v>34042.552900000002</v>
+      </c>
+      <c r="I29">
+        <f>L10</f>
+        <v>225986.2052</v>
+      </c>
+      <c r="J29">
+        <f>N10</f>
+        <v>235402.29790000001</v>
+      </c>
+      <c r="L29">
+        <f>P10</f>
+        <v>830621.04920000001</v>
+      </c>
+      <c r="M29">
+        <f>R10</f>
+        <v>1096378.0903</v>
+      </c>
+      <c r="O29">
+        <f>T10</f>
+        <v>356004.61940000003</v>
+      </c>
+      <c r="P29">
+        <f>V10</f>
+        <v>483326.11969999998</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A30" s="6"/>
+      <c r="B30" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30">
+        <f>D11</f>
+        <v>603.25</v>
+      </c>
+      <c r="D30">
+        <f>F11</f>
+        <v>599.5204</v>
+      </c>
+      <c r="F30">
+        <f>H11</f>
+        <v>35210.784099999997</v>
+      </c>
+      <c r="G30">
+        <f>J11</f>
+        <v>36734.108800000002</v>
+      </c>
+      <c r="I30">
+        <f>L11</f>
+        <v>221106.60949999999</v>
+      </c>
+      <c r="J30">
+        <f>N11</f>
+        <v>246375.94</v>
+      </c>
+      <c r="L30">
+        <f>P11</f>
+        <v>815631.61250000005</v>
+      </c>
+      <c r="M30">
+        <f>R11</f>
+        <v>1065193.0251</v>
+      </c>
+      <c r="O30">
+        <f>T11</f>
+        <v>358966.13630000001</v>
+      </c>
+      <c r="P30">
+        <f>V11</f>
+        <v>479875.52250000002</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A31" s="6"/>
+      <c r="B31" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C31">
+        <f>C29/C28</f>
+        <v>0.48486719851747007</v>
+      </c>
+      <c r="D31">
+        <f>D29/D28</f>
+        <v>0.61782764806245694</v>
+      </c>
+      <c r="F31">
+        <f t="shared" ref="F31" si="56">F29/F28</f>
+        <v>28.323374873953345</v>
+      </c>
+      <c r="G31">
+        <f t="shared" ref="G31" si="57">G29/G28</f>
+        <v>37.32709459855824</v>
+      </c>
+      <c r="I31">
+        <f t="shared" ref="I31" si="58">I29/I28</f>
+        <v>203.22215371798742</v>
+      </c>
+      <c r="J31">
+        <f t="shared" ref="J31" si="59">J29/J28</f>
+        <v>274.10891647572964</v>
+      </c>
+      <c r="L31">
+        <f t="shared" ref="L31" si="60">L29/L28</f>
+        <v>768.24756700792364</v>
+      </c>
+      <c r="M31">
+        <f t="shared" ref="M31" si="61">M29/M28</f>
+        <v>1277.5567117055969</v>
+      </c>
+      <c r="O31">
+        <f>T12</f>
+        <v>320.43357646665544</v>
+      </c>
+      <c r="P31">
+        <f t="shared" ref="P31" si="62">P29/P28</f>
+        <v>560.95571532844428</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A32" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B32" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C24">
-        <f>D8</f>
-        <v>1178.5260000000001</v>
-      </c>
-      <c r="D24">
-        <f>F8</f>
-        <v>890.06020000000001</v>
-      </c>
-      <c r="F24">
-        <f>H8</f>
-        <v>1211.7537</v>
-      </c>
-      <c r="G24">
-        <f>J8</f>
-        <v>912.00649999999996</v>
-      </c>
-      <c r="I24">
-        <f>L8</f>
-        <v>1112.0155999999999</v>
-      </c>
-      <c r="J24">
-        <f>N8</f>
-        <v>858.79110000000003</v>
-      </c>
-      <c r="L24">
-        <f>P8</f>
-        <v>1081.1893</v>
-      </c>
-      <c r="M24">
-        <f>R8</f>
-        <v>858.18349999999998</v>
-      </c>
-      <c r="O24">
-        <v>1111.0091</v>
-      </c>
-      <c r="P24">
-        <f>V8</f>
-        <v>861.61189999999999</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A25" s="4"/>
-      <c r="B25" s="2" t="s">
+      <c r="C32">
+        <f>D13</f>
+        <v>23.9206</v>
+      </c>
+      <c r="D32">
+        <f>F13</f>
+        <v>15.0428</v>
+      </c>
+      <c r="F32">
+        <f>H13</f>
+        <v>23.7059</v>
+      </c>
+      <c r="G32">
+        <f>J13</f>
+        <v>14.9077</v>
+      </c>
+      <c r="I32">
+        <f>L13</f>
+        <v>23.375900000000001</v>
+      </c>
+      <c r="J32">
+        <f>N13</f>
+        <v>14.9817</v>
+      </c>
+      <c r="L32">
+        <f>P13</f>
+        <v>23.613700000000001</v>
+      </c>
+      <c r="M32">
+        <f>R13</f>
+        <v>14.8847</v>
+      </c>
+      <c r="O32">
+        <f>T13</f>
+        <v>23.6295</v>
+      </c>
+      <c r="P32">
+        <f>V13</f>
+        <v>14.9041</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A33" s="6"/>
+      <c r="B33" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33">
+        <f>D14</f>
+        <v>88.514700000000005</v>
+      </c>
+      <c r="D33">
+        <f>F14</f>
+        <v>90.995900000000006</v>
+      </c>
+      <c r="F33">
+        <f>H14</f>
+        <v>3257.4947000000002</v>
+      </c>
+      <c r="G33">
+        <f>J14</f>
+        <v>3476.3243000000002</v>
+      </c>
+      <c r="I33">
+        <f>L14</f>
+        <v>26222.791499999999</v>
+      </c>
+      <c r="J33">
+        <f>N14</f>
+        <v>27997.264899999998</v>
+      </c>
+      <c r="L33">
+        <f>P14</f>
+        <v>32483.7667</v>
+      </c>
+      <c r="M33">
+        <f>R14</f>
+        <v>35223.520400000001</v>
+      </c>
+      <c r="O33">
+        <f>T14</f>
+        <v>32664.190200000001</v>
+      </c>
+      <c r="P33">
+        <f>V14</f>
+        <v>35432.286500000002</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A34" s="6"/>
+      <c r="B34" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34">
+        <f>D15</f>
+        <v>99.727599999999995</v>
+      </c>
+      <c r="D34">
+        <f>F15</f>
+        <v>98.6601</v>
+      </c>
+      <c r="F34">
+        <f>H15</f>
+        <v>2191.6118999999999</v>
+      </c>
+      <c r="G34">
+        <f>J15</f>
+        <v>2190.2806999999998</v>
+      </c>
+      <c r="I34">
+        <f>L15</f>
+        <v>17605.845499999999</v>
+      </c>
+      <c r="J34">
+        <f>N15</f>
+        <v>17655.171999999999</v>
+      </c>
+      <c r="L34">
+        <f>P15</f>
+        <v>20554.832399999999</v>
+      </c>
+      <c r="M34">
+        <f>R15</f>
+        <v>20576.4519</v>
+      </c>
+      <c r="O34">
+        <f>T15</f>
+        <v>20630.2546</v>
+      </c>
+      <c r="P34">
+        <f>V15</f>
+        <v>20638.781900000002</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A35" s="6"/>
+      <c r="B35" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C25">
-        <f>D9</f>
-        <v>571.42859999999996</v>
-      </c>
-      <c r="D25">
-        <f>F9</f>
-        <v>549.90380000000005</v>
-      </c>
-      <c r="F25">
-        <f>H9</f>
-        <v>34320.954299999998</v>
-      </c>
-      <c r="G25">
-        <f>J9</f>
-        <v>34042.552900000002</v>
-      </c>
-      <c r="I25">
-        <f>L9</f>
-        <v>225986.2052</v>
-      </c>
-      <c r="J25">
-        <f>N9</f>
-        <v>235402.29790000001</v>
-      </c>
-      <c r="L25">
-        <f>P9</f>
-        <v>830621.04920000001</v>
-      </c>
-      <c r="M25">
-        <f>R9</f>
-        <v>1096378.0903</v>
-      </c>
-      <c r="O25">
-        <f>T9</f>
-        <v>356004.61940000003</v>
-      </c>
-      <c r="P25">
-        <f>V9</f>
-        <v>483326.11969999998</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A26" s="4"/>
-      <c r="B26" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C26">
-        <f>C25/C24</f>
-        <v>0.48486719851747007</v>
-      </c>
-      <c r="D26">
-        <f>D25/D24</f>
-        <v>0.61782764806245694</v>
-      </c>
-      <c r="F26">
-        <f t="shared" ref="F26" si="56">F25/F24</f>
-        <v>28.323374873953345</v>
-      </c>
-      <c r="G26">
-        <f t="shared" ref="G26" si="57">G25/G24</f>
-        <v>37.32709459855824</v>
-      </c>
-      <c r="I26">
-        <f t="shared" ref="I26" si="58">I25/I24</f>
-        <v>203.22215371798742</v>
-      </c>
-      <c r="J26">
-        <f t="shared" ref="J26" si="59">J25/J24</f>
-        <v>274.10891647572964</v>
-      </c>
-      <c r="L26">
-        <f t="shared" ref="L26" si="60">L25/L24</f>
-        <v>768.24756700792364</v>
-      </c>
-      <c r="M26">
-        <f t="shared" ref="M26" si="61">M25/M24</f>
-        <v>1277.5567117055969</v>
-      </c>
-      <c r="O26">
-        <f>T10</f>
-        <v>320.43357646665544</v>
-      </c>
-      <c r="P26">
-        <f t="shared" ref="P26" si="62">P25/P24</f>
-        <v>560.95571532844428</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C27">
-        <f>D11</f>
-        <v>23.9206</v>
-      </c>
-      <c r="D27">
-        <f>F11</f>
-        <v>15.0428</v>
-      </c>
-      <c r="F27">
-        <f>H11</f>
-        <v>23.7059</v>
-      </c>
-      <c r="G27">
-        <f>J11</f>
-        <v>14.9077</v>
-      </c>
-      <c r="I27">
-        <f>L11</f>
-        <v>23.375900000000001</v>
-      </c>
-      <c r="J27">
-        <f>N11</f>
-        <v>14.9817</v>
-      </c>
-      <c r="L27">
-        <f>P11</f>
-        <v>23.613700000000001</v>
-      </c>
-      <c r="M27">
-        <f>R11</f>
-        <v>14.8847</v>
-      </c>
-      <c r="O27">
-        <f>T11</f>
-        <v>23.6295</v>
-      </c>
-      <c r="P27">
-        <f>V11</f>
-        <v>14.9041</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A28" s="4"/>
-      <c r="B28" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C28">
-        <f>D12</f>
-        <v>88.514700000000005</v>
-      </c>
-      <c r="D28">
-        <f>F12</f>
-        <v>90.995900000000006</v>
-      </c>
-      <c r="F28">
-        <f>H12</f>
-        <v>3257.4947000000002</v>
-      </c>
-      <c r="G28">
-        <f>J12</f>
-        <v>3476.3243000000002</v>
-      </c>
-      <c r="I28">
-        <f>L12</f>
-        <v>26222.791499999999</v>
-      </c>
-      <c r="J28">
-        <f>N12</f>
-        <v>27997.264899999998</v>
-      </c>
-      <c r="L28">
-        <f>P12</f>
-        <v>32483.7667</v>
-      </c>
-      <c r="M28">
-        <f>R12</f>
-        <v>35223.520400000001</v>
-      </c>
-      <c r="O28">
-        <f>T12</f>
-        <v>32664.190200000001</v>
-      </c>
-      <c r="P28">
-        <f>V12</f>
-        <v>35432.286500000002</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A29" s="4"/>
-      <c r="B29" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C29">
-        <f>C28/C27</f>
+      <c r="C35">
+        <f>C33/C32</f>
         <v>3.7003545061578724</v>
       </c>
-      <c r="D29">
-        <f>D28/D27</f>
+      <c r="D35">
+        <f>D33/D32</f>
         <v>6.0491331401068953</v>
       </c>
-      <c r="F29">
-        <f t="shared" ref="F29" si="63">F28/F27</f>
+      <c r="F35">
+        <f t="shared" ref="F35" si="63">F33/F32</f>
         <v>137.41282549913734</v>
       </c>
-      <c r="G29">
-        <f t="shared" ref="G29" si="64">G28/G27</f>
+      <c r="G35">
+        <f t="shared" ref="G35" si="64">G33/G32</f>
         <v>233.18984819925274</v>
       </c>
-      <c r="I29">
-        <f t="shared" ref="I29" si="65">I28/I27</f>
+      <c r="I35">
+        <f t="shared" ref="I35" si="65">I33/I32</f>
         <v>1121.7874605897525</v>
       </c>
-      <c r="J29">
-        <f t="shared" ref="J29" si="66">J28/J27</f>
+      <c r="J35">
+        <f t="shared" ref="J35" si="66">J33/J32</f>
         <v>1868.7642190138636</v>
       </c>
-      <c r="L29">
-        <f t="shared" ref="L29" si="67">L28/L27</f>
+      <c r="L35">
+        <f t="shared" ref="L35" si="67">L33/L32</f>
         <v>1375.6322262076676</v>
       </c>
-      <c r="M29">
-        <f t="shared" ref="M29" si="68">M28/M27</f>
+      <c r="M35">
+        <f t="shared" ref="M35" si="68">M33/M32</f>
         <v>2366.4246105060902</v>
       </c>
-      <c r="O29">
-        <f t="shared" ref="O29" si="69">O28/O27</f>
+      <c r="O35">
+        <f t="shared" ref="O35" si="69">O33/O32</f>
         <v>1382.3479210309147</v>
       </c>
-      <c r="P29">
-        <f t="shared" ref="P29" si="70">P28/P27</f>
+      <c r="P35">
+        <f t="shared" ref="P35" si="70">P33/P32</f>
         <v>2377.3516347850591</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C18:P18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="A24:A26"/>
-    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="C1:V1"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="A24:A27"/>
+    <mergeCell ref="A28:A31"/>
+    <mergeCell ref="A32:A35"/>
     <mergeCell ref="S2:V2"/>
     <mergeCell ref="S3:T3"/>
     <mergeCell ref="U3:V3"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="A13:A16"/>
     <mergeCell ref="K2:N2"/>
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="M3:N3"/>
@@ -1797,12 +2136,12 @@
     <mergeCell ref="O3:P3"/>
     <mergeCell ref="Q3:R3"/>
     <mergeCell ref="C2:F2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="C1:V1"/>
+    <mergeCell ref="C21:P21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="O22:P22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="43" fitToHeight="0" orientation="portrait" r:id="rId1"/>

--- a/run_outputs/results.xlsx
+++ b/run_outputs/results.xlsx
@@ -1826,7 +1826,7 @@
         <v>1096378.0903</v>
       </c>
       <c r="O29">
-        <f>T10</f>
+        <f t="shared" ref="O29:O34" si="56">T10</f>
         <v>356004.61940000003</v>
       </c>
       <c r="P29">
@@ -1872,7 +1872,7 @@
         <v>1065193.0251</v>
       </c>
       <c r="O30">
-        <f>T11</f>
+        <f t="shared" si="56"/>
         <v>358966.13630000001</v>
       </c>
       <c r="P30">
@@ -1894,35 +1894,35 @@
         <v>0.61782764806245694</v>
       </c>
       <c r="F31">
-        <f t="shared" ref="F31" si="56">F29/F28</f>
+        <f t="shared" ref="F31" si="57">F29/F28</f>
         <v>28.323374873953345</v>
       </c>
       <c r="G31">
-        <f t="shared" ref="G31" si="57">G29/G28</f>
+        <f t="shared" ref="G31" si="58">G29/G28</f>
         <v>37.32709459855824</v>
       </c>
       <c r="I31">
-        <f t="shared" ref="I31" si="58">I29/I28</f>
+        <f t="shared" ref="I31" si="59">I29/I28</f>
         <v>203.22215371798742</v>
       </c>
       <c r="J31">
-        <f t="shared" ref="J31" si="59">J29/J28</f>
+        <f t="shared" ref="J31" si="60">J29/J28</f>
         <v>274.10891647572964</v>
       </c>
       <c r="L31">
-        <f t="shared" ref="L31" si="60">L29/L28</f>
+        <f t="shared" ref="L31" si="61">L29/L28</f>
         <v>768.24756700792364</v>
       </c>
       <c r="M31">
-        <f t="shared" ref="M31" si="61">M29/M28</f>
+        <f t="shared" ref="M31" si="62">M29/M28</f>
         <v>1277.5567117055969</v>
       </c>
       <c r="O31">
-        <f>T12</f>
+        <f t="shared" si="56"/>
         <v>320.43357646665544</v>
       </c>
       <c r="P31">
-        <f t="shared" ref="P31" si="62">P29/P28</f>
+        <f t="shared" ref="P31" si="63">P29/P28</f>
         <v>560.95571532844428</v>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
         <v>14.8847</v>
       </c>
       <c r="O32">
-        <f>T13</f>
+        <f t="shared" si="56"/>
         <v>23.6295</v>
       </c>
       <c r="P32">
@@ -2012,7 +2012,7 @@
         <v>35223.520400000001</v>
       </c>
       <c r="O33">
-        <f>T14</f>
+        <f t="shared" si="56"/>
         <v>32664.190200000001</v>
       </c>
       <c r="P33">
@@ -2058,7 +2058,7 @@
         <v>20576.4519</v>
       </c>
       <c r="O34">
-        <f>T15</f>
+        <f t="shared" si="56"/>
         <v>20630.2546</v>
       </c>
       <c r="P34">
@@ -2080,46 +2080,46 @@
         <v>6.0491331401068953</v>
       </c>
       <c r="F35">
-        <f t="shared" ref="F35" si="63">F33/F32</f>
+        <f t="shared" ref="F35" si="64">F33/F32</f>
         <v>137.41282549913734</v>
       </c>
       <c r="G35">
-        <f t="shared" ref="G35" si="64">G33/G32</f>
+        <f t="shared" ref="G35" si="65">G33/G32</f>
         <v>233.18984819925274</v>
       </c>
       <c r="I35">
-        <f t="shared" ref="I35" si="65">I33/I32</f>
+        <f t="shared" ref="I35" si="66">I33/I32</f>
         <v>1121.7874605897525</v>
       </c>
       <c r="J35">
-        <f t="shared" ref="J35" si="66">J33/J32</f>
+        <f t="shared" ref="J35" si="67">J33/J32</f>
         <v>1868.7642190138636</v>
       </c>
       <c r="L35">
-        <f t="shared" ref="L35" si="67">L33/L32</f>
+        <f t="shared" ref="L35" si="68">L33/L32</f>
         <v>1375.6322262076676</v>
       </c>
       <c r="M35">
-        <f t="shared" ref="M35" si="68">M33/M32</f>
+        <f t="shared" ref="M35" si="69">M33/M32</f>
         <v>2366.4246105060902</v>
       </c>
       <c r="O35">
-        <f t="shared" ref="O35" si="69">O33/O32</f>
+        <f t="shared" ref="O35" si="70">O33/O32</f>
         <v>1382.3479210309147</v>
       </c>
       <c r="P35">
-        <f t="shared" ref="P35" si="70">P33/P32</f>
+        <f t="shared" ref="P35" si="71">P33/P32</f>
         <v>2377.3516347850591</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C1:V1"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="C21:P21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="O22:P22"/>
     <mergeCell ref="A24:A27"/>
     <mergeCell ref="A28:A31"/>
     <mergeCell ref="A32:A35"/>
@@ -2136,12 +2136,12 @@
     <mergeCell ref="O3:P3"/>
     <mergeCell ref="Q3:R3"/>
     <mergeCell ref="C2:F2"/>
-    <mergeCell ref="C21:P21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="O22:P22"/>
+    <mergeCell ref="C1:V1"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="43" fitToHeight="0" orientation="portrait" r:id="rId1"/>
